--- a/outputs/17111.xlsx
+++ b/outputs/17111.xlsx
@@ -160,15 +160,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -388,93 +388,93 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="0" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="n">
-        <f aca="false">SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A2,Sheet1!$C:$C,Summary!$B$1,Sheet1!$A:$A,"Completed")+SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A2,Sheet1!$C:$C,Summary!$B$1,Sheet1!$A:$A,"Not Completed")</f>
+      <c r="B2" s="2" t="n">
+        <f aca="false">SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A2,Sheet1!$C:$C,Summary!$B$1,Sheet1!$A:$A,Summary!$F$2)+SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A2,Sheet1!$C:$C,Summary!$B$1,Sheet1!$A:$A,Summary!$F$3)</f>
         <v>200</v>
       </c>
-      <c r="C2" s="1" t="n">
-        <f aca="false">SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A2,Sheet1!$C:$C,Summary!$C$1,Sheet1!$A:$A,"Completed")+SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A2,Sheet1!$C:$C,Summary!$C$1,Sheet1!$A:$A,"Not Completed")</f>
+      <c r="C2" s="2" t="n">
+        <f aca="false">SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A2,Sheet1!$C:$C,Summary!$C$1,Sheet1!$A:$A,Summary!$F$2)+SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A2,Sheet1!$C:$C,Summary!$C$1,Sheet1!$A:$A,Summary!$F$3)</f>
         <v>578</v>
       </c>
-      <c r="F2" s="0" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="n">
-        <f aca="false">SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A3,Sheet1!$C:$C,Summary!$B$1,Sheet1!$A:$A,"Completed")+SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A3,Sheet1!$C:$C,Summary!$B$1,Sheet1!$A:$A,"Not Completed")</f>
+      <c r="B3" s="2" t="n">
+        <f aca="false">SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A3,Sheet1!$C:$C,Summary!$B$1,Sheet1!$A:$A,Summary!$F$2)+SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A3,Sheet1!$C:$C,Summary!$B$1,Sheet1!$A:$A,Summary!$F$3)</f>
         <v>1126</v>
       </c>
-      <c r="C3" s="1" t="n">
-        <f aca="false">SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A3,Sheet1!$C:$C,Summary!$C$1,Sheet1!$A:$A,"Completed")+SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A3,Sheet1!$C:$C,Summary!$C$1,Sheet1!$A:$A,"Not Completed")</f>
+      <c r="C3" s="2" t="n">
+        <f aca="false">SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A3,Sheet1!$C:$C,Summary!$C$1,Sheet1!$A:$A,Summary!$F$2)+SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A3,Sheet1!$C:$C,Summary!$C$1,Sheet1!$A:$A,Summary!$F$3)</f>
         <v>130</v>
       </c>
-      <c r="F3" s="0" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1" t="n">
-        <f aca="false">SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A4,Sheet1!$C:$C,Summary!$B$1,Sheet1!$A:$A,"Completed")+SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A4,Sheet1!$C:$C,Summary!$B$1,Sheet1!$A:$A,"Not Completed")</f>
+      <c r="B4" s="2" t="n">
+        <f aca="false">SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A4,Sheet1!$C:$C,Summary!$B$1,Sheet1!$A:$A,Summary!$F$2)+SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A4,Sheet1!$C:$C,Summary!$B$1,Sheet1!$A:$A,Summary!$F$3)</f>
         <v>954</v>
       </c>
-      <c r="C4" s="1" t="n">
-        <f aca="false">SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A4,Sheet1!$C:$C,Summary!$C$1,Sheet1!$A:$A,"Completed")+SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A4,Sheet1!$C:$C,Summary!$C$1,Sheet1!$A:$A,"Not Completed")</f>
+      <c r="C4" s="2" t="n">
+        <f aca="false">SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A4,Sheet1!$C:$C,Summary!$C$1,Sheet1!$A:$A,Summary!$F$2)+SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A4,Sheet1!$C:$C,Summary!$C$1,Sheet1!$A:$A,Summary!$F$3)</f>
         <v>86</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1" t="n">
-        <f aca="false">SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A5,Sheet1!$C:$C,Summary!$B$1,Sheet1!$A:$A,"Completed")+SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A5,Sheet1!$C:$C,Summary!$B$1,Sheet1!$A:$A,"Not Completed")</f>
+      <c r="B5" s="2" t="n">
+        <f aca="false">SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A5,Sheet1!$C:$C,Summary!$B$1,Sheet1!$A:$A,Summary!$F$2)+SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A5,Sheet1!$C:$C,Summary!$B$1,Sheet1!$A:$A,Summary!$F$3)</f>
         <v>463</v>
       </c>
-      <c r="C5" s="1" t="n">
-        <f aca="false">SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A5,Sheet1!$C:$C,Summary!$C$1,Sheet1!$A:$A,"Completed")+SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A5,Sheet1!$C:$C,Summary!$C$1,Sheet1!$A:$A,"Not Completed")</f>
+      <c r="C5" s="2" t="n">
+        <f aca="false">SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A5,Sheet1!$C:$C,Summary!$C$1,Sheet1!$A:$A,Summary!$F$2)+SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A5,Sheet1!$C:$C,Summary!$C$1,Sheet1!$A:$A,Summary!$F$3)</f>
         <v>775</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="1" t="n">
-        <f aca="false">SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A6,Sheet1!$C:$C,Summary!$B$1,Sheet1!$A:$A,"Completed")+SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A6,Sheet1!$C:$C,Summary!$B$1,Sheet1!$A:$A,"Not Completed")</f>
+      <c r="B6" s="2" t="n">
+        <f aca="false">SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A6,Sheet1!$C:$C,Summary!$B$1,Sheet1!$A:$A,Summary!$F$2)+SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A6,Sheet1!$C:$C,Summary!$B$1,Sheet1!$A:$A,Summary!$F$3)</f>
         <v>96</v>
       </c>
-      <c r="C6" s="1" t="n">
-        <f aca="false">SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A6,Sheet1!$C:$C,Summary!$C$1,Sheet1!$A:$A,"Completed")+SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A6,Sheet1!$C:$C,Summary!$C$1,Sheet1!$A:$A,"Not Completed")</f>
+      <c r="C6" s="2" t="n">
+        <f aca="false">SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A6,Sheet1!$C:$C,Summary!$C$1,Sheet1!$A:$A,Summary!$F$2)+SUMIFS(Sheet1!$D:$D,Sheet1!$B:$B,Summary!$A6,Sheet1!$C:$C,Summary!$C$1,Sheet1!$A:$A,Summary!$F$3)</f>
         <v>108</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="2"/>
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -495,395 +495,395 @@
   <dimension ref="A1:D28"/>
   <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="0" t="s">
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="0" t="n">
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="0" t="s">
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="0" t="n">
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="n">
         <v>130</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="0" t="s">
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="0" t="n">
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="n">
         <v>52</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="0" t="s">
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="0" t="n">
+      <c r="C5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="1" t="n">
         <v>63</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="0" t="s">
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="0" t="n">
+      <c r="C6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="n">
         <v>96</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="0" t="s">
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="0" t="n">
+      <c r="C7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1" t="n">
         <v>78</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="0" t="s">
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="0" t="n">
+      <c r="C8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="n">
         <v>41</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="0" t="s">
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="0" t="n">
+      <c r="C9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>23</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="0" t="s">
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="0" t="n">
+      <c r="C10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>63</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="0" t="s">
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="0" t="n">
+      <c r="C11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>96</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="0" t="s">
+      <c r="C12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D13" s="0" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="0" t="s">
+      <c r="C13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" s="0" t="n">
+      <c r="C14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="0" t="s">
+    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D15" s="0" t="n">
+      <c r="C15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1" t="n">
         <v>85</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="0" t="s">
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="0" t="n">
+      <c r="C16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="1" t="n">
         <v>63</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D17" s="0" t="n">
+      <c r="C17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" s="0" t="s">
+    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D18" s="0" t="n">
+      <c r="C18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="0" t="s">
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D19" s="0" t="n">
+      <c r="C19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>400</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" s="0" t="s">
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D20" s="0" t="n">
+      <c r="C20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D20" s="1" t="n">
         <v>900</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="0" t="s">
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" s="0" t="n">
+      <c r="C21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="1" t="n">
         <v>700</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D22" s="0" t="n">
+      <c r="C22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="1" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" s="0" t="s">
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D23" s="0" t="n">
+      <c r="C23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="1" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" s="0" t="s">
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C24" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D24" s="0" t="n">
+      <c r="C24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" s="1" t="n">
         <v>600</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D25" s="0" t="n">
+      <c r="C25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" s="1" t="n">
         <v>500</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" s="0" t="s">
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D26" s="0" t="n">
+      <c r="C26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D26" s="1" t="n">
         <v>400</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B27" s="0" t="s">
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D27" s="0" t="n">
+      <c r="C27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" s="1" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D28" s="0" t="n">
+      <c r="C28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="1" t="n">
         <v>120</v>
       </c>
     </row>
